--- a/output/pdf_financials_xlsx/JOLT.xlsx
+++ b/output/pdf_financials_xlsx/JOLT.xlsx
@@ -1984,13 +1984,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.274928</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.524928</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.524928</v>
       </c>
     </row>
     <row r="93">
@@ -3130,7 +3130,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>-</t>
@@ -3366,7 +3370,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E19" s="5" t="n">
         <v>1.274928</v>
       </c>

--- a/output/pdf_financials_xlsx/JOLT.xlsx
+++ b/output/pdf_financials_xlsx/JOLT.xlsx
@@ -589,10 +589,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.250917</v>
+        <v>0.430574</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.782533</v>
+        <v>0.887244</v>
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
@@ -607,10 +607,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.250917</v>
+        <v>-0.430574</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.782533</v>
+        <v>-0.887244</v>
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
@@ -1026,13 +1026,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.002059</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.000851</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.000561</v>
       </c>
     </row>
     <row r="35">
@@ -1058,13 +1058,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.002059</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.000851</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.000561</v>
       </c>
     </row>
     <row r="37">
@@ -1250,13 +1250,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.014759</v>
+        <v>0.0127</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.933267</v>
+        <v>0.932416</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.773053</v>
+        <v>0.772492</v>
       </c>
     </row>
     <row r="49">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E53" s="5" t="n">
@@ -4574,7 +4574,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E57" s="5" t="n">

--- a/output/pdf_financials_xlsx/JOLT.xlsx
+++ b/output/pdf_financials_xlsx/JOLT.xlsx
@@ -486,10 +486,8 @@
       <c r="C4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D4" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -504,10 +502,8 @@
       <c r="C5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -522,10 +518,8 @@
       <c r="C6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D6" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -540,10 +534,8 @@
       <c r="C7" s="3" t="n">
         <v>0.7717349999999999</v>
       </c>
-      <c r="D7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D7" s="3" t="n">
+        <v>0.541578</v>
       </c>
     </row>
     <row r="8">
@@ -558,10 +550,8 @@
       <c r="C8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D8" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -576,10 +566,8 @@
       <c r="C9" s="3" t="n">
         <v>0.010798</v>
       </c>
-      <c r="D9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D9" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -594,10 +582,8 @@
       <c r="C10" s="3" t="n">
         <v>0.887244</v>
       </c>
-      <c r="D10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D10" s="3" t="n">
+        <v>0.604286</v>
       </c>
     </row>
     <row r="11">
@@ -612,10 +598,8 @@
       <c r="C11" s="3" t="n">
         <v>-0.887244</v>
       </c>
-      <c r="D11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D11" s="3" t="n">
+        <v>-0.604286</v>
       </c>
     </row>
     <row r="12">
@@ -630,10 +614,8 @@
       <c r="C12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D12" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -648,10 +630,8 @@
       <c r="C13" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="D13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D13" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -666,10 +646,8 @@
       <c r="C14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D14" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -682,12 +660,10 @@
         <v>-0.023621</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>-0.006916</v>
-      </c>
-      <c r="D15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.006916</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>-1e-05</v>
       </c>
     </row>
     <row r="16">
@@ -700,12 +676,10 @@
         <v>-0.7657350000000001</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-0.7657350000000001</v>
-      </c>
-      <c r="D16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.169524</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>-0.519535</v>
       </c>
     </row>
     <row r="17">
@@ -720,10 +694,8 @@
       <c r="C17" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="D17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D17" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="18">
@@ -780,12 +752,10 @@
         <v>-0.7657350000000001</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>-0.7657350000000001</v>
-      </c>
-      <c r="D20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.169524</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>-0.519535</v>
       </c>
     </row>
     <row r="21">
@@ -800,10 +770,8 @@
       <c r="C21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -818,10 +786,8 @@
       <c r="C22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D22" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -834,12 +800,10 @@
         <v>-0.7657350000000001</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>-0.7657350000000001</v>
-      </c>
-      <c r="D23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.169524</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>-0.519535</v>
       </c>
     </row>
     <row r="24">
@@ -854,10 +818,8 @@
       <c r="C24" s="3" t="n">
         <v>-0.2</v>
       </c>
-      <c r="D24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D24" s="3" t="n">
+        <v>-0.06</v>
       </c>
     </row>
     <row r="25">
@@ -872,10 +834,8 @@
       <c r="C25" s="3" t="n">
         <v>-0.2</v>
       </c>
-      <c r="D25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D25" s="3" t="n">
+        <v>-0.06</v>
       </c>
     </row>
     <row r="26">
@@ -888,12 +848,10 @@
         <v>3.190562</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>3.828675</v>
-      </c>
-      <c r="D26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>5.84762</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>8.658917000000001</v>
       </c>
     </row>
     <row r="27">
@@ -906,12 +864,10 @@
         <v>-0.7657350000000001</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.7657350000000001</v>
-      </c>
-      <c r="D27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.169524</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>-0.519535</v>
       </c>
     </row>
     <row r="28">
@@ -926,10 +882,8 @@
       <c r="C28" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D28" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -942,12 +896,10 @@
         <v>-0.7657350000000001</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.7657350000000001</v>
-      </c>
-      <c r="D29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.169524</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>-0.519535</v>
       </c>
     </row>
     <row r="30">
@@ -984,10 +936,8 @@
       <c r="C31" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="D31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D31" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -1560,13 +1510,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.045</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.055</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.045</v>
       </c>
     </row>
     <row r="68">
@@ -2110,10 +2060,8 @@
       <c r="C99" s="3" t="n">
         <v>-1.169524</v>
       </c>
-      <c r="D99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D99" s="3" t="n">
+        <v>-0.519535</v>
       </c>
     </row>
     <row r="100">
@@ -2128,10 +2076,8 @@
       <c r="C100" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D100" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -2146,10 +2092,8 @@
       <c r="C101" s="3" t="n">
         <v>6.600000000000001e-05</v>
       </c>
-      <c r="D101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D101" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -2164,10 +2108,8 @@
       <c r="C102" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D102" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -2182,10 +2124,8 @@
       <c r="C103" s="3" t="n">
         <v>-0.012274</v>
       </c>
-      <c r="D103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D103" s="3" t="n">
+        <v>0.011165</v>
       </c>
     </row>
     <row r="104">
@@ -2200,10 +2140,8 @@
       <c r="C104" s="3" t="n">
         <v>0.404923</v>
       </c>
-      <c r="D104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D104" s="3" t="n">
+        <v>0.50108</v>
       </c>
     </row>
     <row r="105">
@@ -2218,10 +2156,8 @@
       <c r="C105" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D105" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -2236,10 +2172,8 @@
       <c r="C106" s="3" t="n">
         <v>0.392715</v>
       </c>
-      <c r="D106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D106" s="3" t="n">
+        <v>0.512245</v>
       </c>
     </row>
     <row r="107">
@@ -2254,10 +2188,8 @@
       <c r="C107" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D107" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -2272,10 +2204,8 @@
       <c r="C108" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D108" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -2290,10 +2220,8 @@
       <c r="C109" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D109" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -2308,10 +2236,8 @@
       <c r="C110" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D110" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -2326,10 +2252,8 @@
       <c r="C111" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D111" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -2344,10 +2268,8 @@
       <c r="C112" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D112" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -2362,10 +2284,8 @@
       <c r="C113" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D113" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -2380,10 +2300,8 @@
       <c r="C114" s="3" t="n">
         <v>-0.25</v>
       </c>
-      <c r="D114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D114" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -2398,10 +2316,8 @@
       <c r="C115" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D115" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -2416,10 +2332,8 @@
       <c r="C116" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D116" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -2434,10 +2348,8 @@
       <c r="C117" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D117" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -2452,10 +2364,8 @@
       <c r="C118" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D118" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -2470,10 +2380,8 @@
       <c r="C119" s="3" t="n">
         <v>-0.01</v>
       </c>
-      <c r="D119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D119" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -2488,10 +2396,8 @@
       <c r="C120" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D120" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -2506,10 +2412,8 @@
       <c r="C121" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D121" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -2524,10 +2428,8 @@
       <c r="C122" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D122" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -2542,10 +2444,8 @@
       <c r="C123" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D123" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -2560,10 +2460,8 @@
       <c r="C124" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D124" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -2578,10 +2476,8 @@
       <c r="C125" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D125" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -2596,10 +2492,8 @@
       <c r="C126" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D126" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -2636,10 +2530,8 @@
       <c r="C128" s="3" t="n">
         <v>-0.0155</v>
       </c>
-      <c r="D128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D128" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -2654,10 +2546,8 @@
       <c r="C129" s="3" t="n">
         <v>0.514</v>
       </c>
-      <c r="D129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D129" s="3" t="n">
+        <v>0.07065399999999999</v>
       </c>
     </row>
     <row r="130">
@@ -2694,10 +2584,8 @@
       <c r="C131" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D131" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -2712,10 +2600,8 @@
       <c r="C132" s="3" t="n">
         <v>-0.001208</v>
       </c>
-      <c r="D132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D132" s="3" t="n">
+        <v>-0.00029</v>
       </c>
     </row>
     <row r="133">
@@ -2752,10 +2638,8 @@
       <c r="C134" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D134" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -2770,10 +2654,8 @@
       <c r="C135" s="3" t="n">
         <v>-0.505208</v>
       </c>
-      <c r="D135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D135" s="3" t="n">
+        <v>-0.07094399999999999</v>
       </c>
     </row>
   </sheetData>
@@ -2787,7 +2669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G76"/>
+  <dimension ref="A1:G90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3464,10 +3346,8 @@
       <c r="F22" s="5" t="n">
         <v>-1.169524</v>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G22" s="5" t="n">
+        <v>-0.519535</v>
       </c>
     </row>
     <row r="23">
@@ -3483,22 +3363,18 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Accrued interest</t>
+          <t>Unrealized foreign exchange</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" s="5" t="n">
-        <v>0.002383</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.00702</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-0.009396</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-1e-05</v>
       </c>
     </row>
     <row r="24">
@@ -3514,17 +3390,15 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Accretion and interest on convertible debenture</t>
+          <t>Fair value adjustment of investments</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" s="5" t="n">
-        <v>0.014833</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.259398</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>0.270997</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -3545,26 +3419,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Share-based payments</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="n">
-        <v>0.063</v>
+          <t>Gain on settlement of debt</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G25" s="5" t="n">
+        <v>-0.06364400000000001</v>
       </c>
     </row>
     <row r="26">
@@ -3580,15 +3450,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Unrealized foreign exchange</t>
+          <t>Realized loss on investment</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" s="5" t="n">
-        <v>-0.00702</v>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>-0.009396</v>
+        <v>0.01</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -3609,22 +3481,26 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Impairment of intangible asset</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" s="5" t="n">
-        <v>0.1</v>
+          <t>Write-off of accounts payable</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G27" s="5" t="n">
+        <v>-0.014647</v>
       </c>
     </row>
     <row r="28">
@@ -3635,25 +3511,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Adjusted for</t>
+          <t>Changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Fair value adjustment of investments</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>Prepaid expenses and deposits</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E28" s="5" t="n">
-        <v>0.259398</v>
+        <v>0.051264</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>0.270997</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.012274</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>0.011165</v>
       </c>
     </row>
     <row r="29">
@@ -3664,22 +3542,24 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Adjusted for</t>
+          <t>Changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Realized loss on investment</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Receivables</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>0.00567</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>0.01</v>
+        <v>6.600000000000001e-05</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -3695,27 +3575,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Adjusted for</t>
+          <t>Changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Fair value adjustment - derivative liability</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
+          <t>Accounts payable and accrued liabilities</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E30" s="5" t="n">
-        <v>-0.003</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.157132</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>0.404923</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0.515727</v>
       </c>
     </row>
     <row r="31">
@@ -3731,24 +3611,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Prepaid expenses and deposits</t>
+          <t>Cash flows from operating activities</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ChangeInPrepaidAssets</t>
+          <t>OperatingCashFlow</t>
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>0.051264</v>
+        <v>-0.122075</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>-0.012274</v>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.505208</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>-0.07094399999999999</v>
       </c>
     </row>
     <row r="32">
@@ -3759,24 +3637,26 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Receivables</t>
+          <t>Purchase of investment</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ChangeInReceivables</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="n">
-        <v>0.00567</v>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>6.600000000000001e-05</v>
+        <v>-0.25</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -3792,24 +3672,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="n">
-        <v>0.157132</v>
+          <t>Proceeds on refund of deposit on investment</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>0.404923</v>
+        <v>0.24</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -3825,24 +3703,26 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Cash flows from operating activities</t>
+          <t>Cash flows from investing activities</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="n">
-        <v>-0.122075</v>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>-0.505208</v>
+        <v>-0.01</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -3858,26 +3738,20 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Purchase of investment</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>PurchaseOfInvestment</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Units issued for cash</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" s="5" t="n">
+        <v>0.09987500000000001</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>-0.25</v>
+        <v>0.5</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -3893,22 +3767,26 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Proceeds on refund of deposit on investment</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
+          <t>Share issue costs</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F36" s="5" t="n">
-        <v>0.24</v>
+        <v>-0.0155</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -3924,17 +3802,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cash flows from investing activities</t>
+          <t>Proceeds from loan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>InvestingCashFlow</t>
+          <t>ProceedsFromLoans</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3943,12 +3821,10 @@
         </is>
       </c>
       <c r="F37" s="5" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.0295</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>0.07065399999999999</v>
       </c>
     </row>
     <row r="38">
@@ -3964,20 +3840,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Units issued for cash</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
+          <t>Cash flows from financing activities</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
       <c r="E38" s="5" t="n">
-        <v>0.09987500000000001</v>
+        <v>0.082526</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.514</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>0.07065399999999999</v>
       </c>
     </row>
     <row r="39">
@@ -3993,24 +3871,24 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Share issuance costs</t>
+          <t>Change in cash $</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NetOtherFinancingCharges</t>
-        </is>
-      </c>
-      <c r="E39" s="5" t="n">
-        <v>-0.017349</v>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F39" s="5" t="n">
-        <v>-0.0155</v>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.001208</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>-0.00029</v>
       </c>
     </row>
     <row r="40">
@@ -4026,26 +3904,18 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Proceeds from loan</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>ProceedsFromLoans</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash, beginning</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" s="5" t="n">
+        <v>0.041608</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>0.0295</v>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002059</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>0.000851</v>
       </c>
     </row>
     <row r="41">
@@ -4061,24 +3931,20 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Cash flows from financing activities</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
-      <c r="E41" s="5" t="n">
-        <v>0.082526</v>
+          <t>Cash, end $</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F41" s="5" t="n">
-        <v>0.514</v>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.000851</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>0.000561</v>
       </c>
     </row>
     <row r="42">
@@ -4089,24 +3955,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Adjusted for</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Change in cash</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
+          <t>Accrued interest</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" s="5" t="n">
-        <v>-0.039549</v>
-      </c>
-      <c r="F42" s="5" t="n">
-        <v>-0.001208</v>
+        <v>0.002383</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -4122,20 +3986,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Adjusted for</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Cash, beginning</t>
+          <t>Accretion and interest on convertible debenture</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" s="5" t="n">
-        <v>0.041608</v>
-      </c>
-      <c r="F43" s="5" t="n">
-        <v>0.002059</v>
+        <v>0.014833</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -4151,20 +4017,26 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Adjusted for</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Cash, end</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
+          <t>Share-based payments</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E44" s="5" t="n">
-        <v>0.002059</v>
-      </c>
-      <c r="F44" s="5" t="n">
-        <v>0.000851</v>
+        <v>0.063</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -4175,22 +4047,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Adjusted for</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Accretion and interest on convertible debenture 8 $</t>
+          <t>Impairment of intangible asset</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" s="5" t="n">
-        <v>0.014833</v>
+        <v>0.1</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4206,29 +4078,27 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Adjusted for</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Advertising and promotion</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
+          <t>Fair value adjustment - derivative liability</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
       <c r="E46" s="5" t="n">
-        <v>0.051788</v>
-      </c>
-      <c r="F46" s="5" t="n">
-        <v>0.010798</v>
+        <v>-0.003</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -4239,29 +4109,29 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Consulting and management fees 10</t>
+          <t>Share issuance costs</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>NetOtherFinancingCharges</t>
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>0.1414</v>
+        <v>-0.017349</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>0.708935</v>
+        <v>-0.0155</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -4272,29 +4142,29 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Office and general</t>
+          <t>Change in cash</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>ChangesInCash</t>
         </is>
       </c>
       <c r="E48" s="5" t="n">
-        <v>0.018103</v>
+        <v>-0.039549</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>0.036455</v>
+        <v>-0.001208</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -4305,29 +4175,25 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>Cash, end</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
       <c r="E49" s="5" t="n">
-        <v>0.09951699999999999</v>
+        <v>0.002059</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>0.103025</v>
+        <v>0.000851</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -4348,17 +4214,21 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Share-based payments 9, 10</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" s="5" t="n">
-        <v>0.063</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Advertising and promotion $</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="n">
+        <v>0.010798</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -4379,7 +4249,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Transfer agent and filing fees</t>
+          <t>Consulting and management fees</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4387,16 +4257,16 @@
           <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
-      <c r="E51" s="5" t="n">
-        <v>0.039626</v>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F51" s="5" t="n">
-        <v>0.026345</v>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.708935</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>0.51153</v>
       </c>
     </row>
     <row r="52">
@@ -4412,20 +4282,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Travel and entertainment</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
+          <t>Office and general</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E52" s="5" t="n">
-        <v>0.002307</v>
+        <v>0.018103</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>0.001686</v>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.036455</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>0.002957</v>
       </c>
     </row>
     <row r="53">
@@ -4441,24 +4313,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Total expenses</t>
+          <t>Professional fees</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>0.430574</v>
+        <v>0.09951699999999999</v>
       </c>
       <c r="F53" s="5" t="n">
-        <v>0.887244</v>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.103025</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>0.062708</v>
       </c>
     </row>
     <row r="54">
@@ -4474,17 +4344,15 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Fair value adjustment - derivative liability 8</t>
+          <t>Travel and entertainment</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" s="5" t="n">
-        <v>-0.003</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002307</v>
+      </c>
+      <c r="F54" s="5" t="n">
+        <v>0.001686</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -4505,24 +4373,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Foreign exchange gain</t>
+          <t>Transfer agent and filing fees</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>-0.007131</v>
+        <v>0.039626</v>
       </c>
       <c r="F55" s="5" t="n">
-        <v>-0.006916</v>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.026345</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>0.027091</v>
       </c>
     </row>
     <row r="56">
@@ -4538,22 +4404,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Impairment of intangible asset 5</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
+          <t>Total expenses</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E56" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.430574</v>
+      </c>
+      <c r="F56" s="5" t="n">
+        <v>0.887244</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>0.604286</v>
       </c>
     </row>
     <row r="57">
@@ -4569,24 +4435,24 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Interest expense</t>
+          <t>Foreign exchange gain (loss)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>InterestExpenseOperating</t>
-        </is>
-      </c>
-      <c r="E57" s="5" t="n">
-        <v>0.002384</v>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F57" s="5" t="n">
-        <v>0.008199</v>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.006916</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>-1e-05</v>
       </c>
     </row>
     <row r="58">
@@ -4602,20 +4468,20 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Fair value adjustment of investments 4</t>
+          <t>Interest recovery (expense)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
-      <c r="E58" s="5" t="n">
-        <v>0.259398</v>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F58" s="5" t="n">
-        <v>0.270997</v>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.008199</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0.00647</v>
       </c>
     </row>
     <row r="59">
@@ -4631,7 +4497,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Realized loss on investments 4</t>
+          <t>Fair value adjustment of investments</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
@@ -4641,7 +4507,7 @@
         </is>
       </c>
       <c r="F59" s="5" t="n">
-        <v>0.01</v>
+        <v>-0.270997</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -4662,26 +4528,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Other income</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
-      <c r="E60" s="5" t="n">
-        <v>-0.01649</v>
+          <t>Gain on settlement of debt</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G60" s="5" t="n">
+        <v>0.06364400000000001</v>
       </c>
     </row>
     <row r="61">
@@ -4697,19 +4559,17 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss $</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E61" s="5" t="n">
-        <v>-0.7657350000000001</v>
+          <t>Realized loss on investments</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F61" s="5" t="n">
-        <v>-1.169524</v>
+        <v>-0.01</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -4725,29 +4585,27 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Loss per share</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Basic and diluted $</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E62" s="5" t="n">
-        <v>-2.4e-07</v>
-      </c>
-      <c r="F62" s="5" t="n">
-        <v>-2e-07</v>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Write-off of accounts payable</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>0.014647</v>
       </c>
     </row>
     <row r="63">
@@ -4758,25 +4616,27 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Basic and diluted</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr"/>
+          <t>Loss and comprehensive loss $</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E63" s="5" t="n">
-        <v>3.258331</v>
+        <v>-0.7657350000000001</v>
       </c>
       <c r="F63" s="5" t="n">
-        <v>5.770115</v>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.169524</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>-0.519535</v>
       </c>
     </row>
     <row r="64">
@@ -4787,25 +4647,27 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>shares     Share Capital         Reserves             Deficit       (Deficiency)</t>
+          <t>Loss per share</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2022 2,521,141 $ 12,235,260 $ 1,210,928 $</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr"/>
+          <t>Basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E64" s="5" t="n">
-        <v>0.187805</v>
+        <v>-2.4e-07</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>-13.258383</v>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2e-07</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>-5.999999999999999e-08</v>
       </c>
     </row>
     <row r="65">
@@ -4816,27 +4678,23 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>shares     Share Capital         Reserves             Deficit       (Deficiency)</t>
+          <t>Weighted average number of common shares</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Units issued for cash 349,213 99,875 -</t>
+          <t>Basic and diluted</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" s="5" t="n">
-        <v>0.09987500000000001</v>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.258331</v>
+      </c>
+      <c r="F65" s="5" t="n">
+        <v>5.770115</v>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v>8.439337999999999</v>
       </c>
     </row>
     <row r="66">
@@ -4847,27 +4705,25 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>shares     Share Capital         Reserves             Deficit       (Deficiency)</t>
+          <t>Deficit(14,024,118)--(1,169,524)(15,193,642)-(519,535)(15,713,177)</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Share issuance costs – cash - (17,349) -</t>
+          <t>Deficit(14,024,118)--(1,169,524)(15,193,642)-(519,535)(15,713,177) statements. Reserves 250,000-- -- 1,274,928</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
-      <c r="E66" s="5" t="n">
-        <v>-0.017349</v>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F66" s="5" t="n">
+        <v>1.524928</v>
+      </c>
+      <c r="G66" s="5" t="n">
+        <v>1.524928</v>
       </c>
     </row>
     <row r="67">
@@ -4878,19 +4734,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>shares     Share Capital         Reserves             Deficit       (Deficiency)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Share issuance costs – broker warrants - (1,000) 1,000</t>
+          <t>Accretion and interest on convertible debenture 8 $</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E67" s="5" t="n">
+        <v>0.014833</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -4911,22 +4765,24 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>shares     Share Capital         Reserves             Deficit       (Deficiency)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Conversion of convertible debenture 688,288 213,733 -</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
+          <t>Advertising and promotion</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E68" s="5" t="n">
-        <v>0.213733</v>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.051788</v>
+      </c>
+      <c r="F68" s="5" t="n">
+        <v>0.010798</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -4942,22 +4798,24 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>shares     Share Capital         Reserves             Deficit       (Deficiency)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Common shares issued for debt 305,844 91,753 -</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr"/>
+          <t>Consulting and management fees 10</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E69" s="5" t="n">
-        <v>0.091753</v>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.1414</v>
+      </c>
+      <c r="F69" s="5" t="n">
+        <v>0.708935</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -4973,12 +4831,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>shares     Share Capital         Reserves             Deficit       (Deficiency)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Share-based payments - - 63,000</t>
+          <t>Share-based payments 9, 10</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -5004,24 +4862,22 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>shares     Share Capital         Reserves             Deficit       (Deficiency)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the year - -</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Fair value adjustment - derivative liability 8</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
       <c r="E71" s="5" t="n">
-        <v>-0.7657350000000001</v>
-      </c>
-      <c r="F71" s="5" t="n">
-        <v>-0.7657350000000001</v>
+        <v>-0.003</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -5037,20 +4893,24 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>shares     Share Capital         Reserves             Deficit       (Deficiency)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2023 3,864,486 12,622,272 1,274,928</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr"/>
+          <t>Foreign exchange gain</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E72" s="5" t="n">
-        <v>-0.126918</v>
+        <v>-0.007131</v>
       </c>
       <c r="F72" s="5" t="n">
-        <v>-14.024118</v>
+        <v>-0.006916</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -5066,17 +4926,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>shares     Share Capital         Reserves             Deficit       (Deficiency)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Units issued for cash 2,500,000 250,000 250,000</t>
+          <t>Impairment of intangible asset 5</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" s="5" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5097,22 +4957,24 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>shares     Share Capital         Reserves             Deficit       (Deficiency)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Share issuance costs – cash - (15,500) -</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr"/>
+          <t>Interest expense</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
       <c r="E74" s="5" t="n">
-        <v>-0.0155</v>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002384</v>
+      </c>
+      <c r="F74" s="5" t="n">
+        <v>0.008199</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -5128,24 +4990,20 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>shares     Share Capital         Reserves             Deficit       (Deficiency)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Net and comprehensive loss for the year - - -</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Fair value adjustment of investments 4</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
       <c r="E75" s="5" t="n">
-        <v>-1.169524</v>
+        <v>0.259398</v>
       </c>
       <c r="F75" s="5" t="n">
-        <v>-1.169524</v>
+        <v>0.270997</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -5161,22 +5019,462 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Realized loss on investments 4</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F76" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Other income</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="n">
+        <v>-0.01649</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
           <t>shares     Share Capital         Reserves             Deficit       (Deficiency)</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Balance, December 31, 2022 2,521,141 $ 12,235,260 $ 1,210,928 $</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" s="5" t="n">
+        <v>0.187805</v>
+      </c>
+      <c r="F78" s="5" t="n">
+        <v>-13.258383</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>shares     Share Capital         Reserves             Deficit       (Deficiency)</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Units issued for cash 349,213 99,875 -</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" s="5" t="n">
+        <v>0.09987500000000001</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>shares     Share Capital         Reserves             Deficit       (Deficiency)</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Share issuance costs – cash - (17,349) -</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" s="5" t="n">
+        <v>-0.017349</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>shares     Share Capital         Reserves             Deficit       (Deficiency)</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Share issuance costs – broker warrants - (1,000) 1,000</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>shares     Share Capital         Reserves             Deficit       (Deficiency)</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Conversion of convertible debenture 688,288 213,733 -</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" s="5" t="n">
+        <v>0.213733</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>shares     Share Capital         Reserves             Deficit       (Deficiency)</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Common shares issued for debt 305,844 91,753 -</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" s="5" t="n">
+        <v>0.091753</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>shares     Share Capital         Reserves             Deficit       (Deficiency)</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Share-based payments - - 63,000</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" s="5" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>shares     Share Capital         Reserves             Deficit       (Deficiency)</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Loss and comprehensive loss for the year - -</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="n">
+        <v>-0.7657350000000001</v>
+      </c>
+      <c r="F85" s="5" t="n">
+        <v>-0.7657350000000001</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>shares     Share Capital         Reserves             Deficit       (Deficiency)</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Balance, December 31, 2023 3,864,486 12,622,272 1,274,928</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" s="5" t="n">
+        <v>-0.126918</v>
+      </c>
+      <c r="F86" s="5" t="n">
+        <v>-14.024118</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>shares     Share Capital         Reserves             Deficit       (Deficiency)</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Units issued for cash 2,500,000 250,000 250,000</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>shares     Share Capital         Reserves             Deficit       (Deficiency)</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Share issuance costs – cash - (15,500) -</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" s="5" t="n">
+        <v>-0.0155</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>shares     Share Capital         Reserves             Deficit       (Deficiency)</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Net and comprehensive loss for the year - - -</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E89" s="5" t="n">
+        <v>-1.169524</v>
+      </c>
+      <c r="F89" s="5" t="n">
+        <v>-1.169524</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>shares     Share Capital         Reserves             Deficit       (Deficiency)</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
         <is>
           <t>Balance, December 31, 2024 6,364,486 $ 12,856,772 $ 1,524,928 $</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" s="5" t="n">
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" s="5" t="n">
         <v>-0.8119420000000001</v>
       </c>
-      <c r="F76" s="5" t="n">
+      <c r="F90" s="5" t="n">
         <v>-15.193642</v>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="G90" t="inlineStr">
         <is>
           <t>-</t>
         </is>
